--- a/artfynd/A 42090-2024 artfynd.xlsx
+++ b/artfynd/A 42090-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143924</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>131143904</v>
       </c>
       <c r="B4" t="n">
-        <v>91773</v>
+        <v>91776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131143905</v>
       </c>
       <c r="B7" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131143909</v>
       </c>
       <c r="B9" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>131143923</v>
       </c>
       <c r="B11" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42090-2024 artfynd.xlsx
+++ b/artfynd/A 42090-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143924</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131143940</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>131143904</v>
       </c>
       <c r="B4" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>131143936</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>131143939</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131143905</v>
       </c>
       <c r="B7" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>131143938</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131143909</v>
       </c>
       <c r="B9" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>131143941</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>131143923</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42090-2024 artfynd.xlsx
+++ b/artfynd/A 42090-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143924</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131143940</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>131143904</v>
       </c>
       <c r="B4" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>131143936</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>131143939</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131143905</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>131143938</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131143909</v>
       </c>
       <c r="B9" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>131143941</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>131143923</v>
       </c>
       <c r="B11" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42090-2024 artfynd.xlsx
+++ b/artfynd/A 42090-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143924</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131143940</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>131143904</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>131143936</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>131143939</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131143905</v>
       </c>
       <c r="B7" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>131143938</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131143909</v>
       </c>
       <c r="B9" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>131143941</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>131143923</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42090-2024 artfynd.xlsx
+++ b/artfynd/A 42090-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143924</v>
       </c>
       <c r="B2" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131143940</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>131143904</v>
       </c>
       <c r="B4" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>131143936</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>131143939</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>131143905</v>
       </c>
       <c r="B7" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>131143938</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131143909</v>
       </c>
       <c r="B9" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>131143941</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>131143923</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42090-2024 artfynd.xlsx
+++ b/artfynd/A 42090-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143936</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143938</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143939</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143940</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143941</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>